--- a/finance/_refresh_line-man-wongnai.xlsx
+++ b/finance/_refresh_line-man-wongnai.xlsx
@@ -6721,7 +6721,7 @@
     <row r="27">
       <c r="A27" s="29" t="inlineStr">
         <is>
-          <t>Eastern_Seaboard</t>
+          <t>Phuket</t>
         </is>
       </c>
       <c r="B27" s="29" t="inlineStr">
@@ -6731,23 +6731,23 @@
       </c>
       <c r="C27" s="30" t="inlineStr">
         <is>
-          <t>Bangkok (Chao Phraya / Gulf gateway) → Pattaya (Bali Hai Pier)</t>
+          <t>Phuket → Similan / Surin Islands</t>
         </is>
       </c>
       <c r="D27" s="31" t="n">
-        <v>52.6</v>
+        <v>55</v>
       </c>
       <c r="E27" s="26" t="n">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="F27" s="32" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="G27" s="32" t="inlineStr">
         <is>
-          <t>low-med</t>
+          <t>med</t>
         </is>
       </c>
       <c r="H27" s="19" t="n">
@@ -6850,16 +6850,16 @@
         <v/>
       </c>
       <c r="AG27" s="31" t="n">
-        <v>148000</v>
+        <v>580000</v>
       </c>
       <c r="AH27" s="32" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="AI27" s="32" t="inlineStr">
         <is>
-          <t>low-med</t>
+          <t>low</t>
         </is>
       </c>
       <c r="AJ27" s="39" t="n">
@@ -6908,19 +6908,19 @@
       </c>
       <c r="AX27" s="44" t="inlineStr">
         <is>
-          <t>Premium slice of Bangkok-Pattaya leisure+EEC road flow; modeled pending operator validation.</t>
+          <t>Phuket-&gt;Similan/Surin premium shared speedboat day-tour (THB/USD 36): premium catamaran-speedboat tours ~2,500-2,600 THB incl 500 THB park fee+meals from Khao Lak (phiphitours 2,590 THB=$72); Phuket-origin runs higher ~2,900-3,500 THB ($80-97) for the longer 55nm leg. Private charter Phuket-&gt;Similan 50,000-80,000 THB/boat/day (forbesandpartners) = whole-boat, excluded. Premium per-seat anchored ~2,900 THB ($80) net for the longer Phuket origin.</t>
         </is>
       </c>
       <c r="AY27" s="44" t="inlineStr">
         <is>
-          <t>Premium slice of Bangkok-Pattaya leisure+EEC road flow; modeled pending operator validation.</t>
+          <t>Mu Ko Similan NP official visitor statistics (DNP/park clarification, May-2025, via MGR Online https://mgronline.com/uptodate/detail/9680000041761): FY2561(2018)=912,566; FY2562(2019)=676,793; FY2566(2023)=352,701; FY2567(2024)=578,535; FY2568=503,142 as of 30-Apr-2025. Daily cap 3,850 visitors/day (DNP, http://news.dnp.go.th/news/7966). Season: park CLOSED ~May 16 - Oct 14; open season ~212 days/yr (reopened 15-Oct each year, prd.go.th).</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="29" t="inlineStr">
         <is>
-          <t>Phuket</t>
+          <t>Eastern_Seaboard</t>
         </is>
       </c>
       <c r="B28" s="29" t="inlineStr">
@@ -6930,23 +6930,23 @@
       </c>
       <c r="C28" s="30" t="inlineStr">
         <is>
-          <t>Phuket → Similan / Surin Islands</t>
+          <t>Bangkok (Chao Phraya / Gulf gateway) → Pattaya (Bali Hai Pier)</t>
         </is>
       </c>
       <c r="D28" s="31" t="n">
-        <v>55</v>
+        <v>55.6</v>
       </c>
       <c r="E28" s="26" t="n">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="F28" s="32" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="G28" s="32" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>low-med</t>
         </is>
       </c>
       <c r="H28" s="19" t="n">
@@ -7049,16 +7049,16 @@
         <v/>
       </c>
       <c r="AG28" s="31" t="n">
-        <v>580000</v>
+        <v>148000</v>
       </c>
       <c r="AH28" s="32" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="AI28" s="32" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>low-med</t>
         </is>
       </c>
       <c r="AJ28" s="39" t="n">
@@ -7107,12 +7107,12 @@
       </c>
       <c r="AX28" s="44" t="inlineStr">
         <is>
-          <t>Phuket-&gt;Similan/Surin premium shared speedboat day-tour (THB/USD 36): premium catamaran-speedboat tours ~2,500-2,600 THB incl 500 THB park fee+meals from Khao Lak (phiphitours 2,590 THB=$72); Phuket-origin runs higher ~2,900-3,500 THB ($80-97) for the longer 55nm leg. Private charter Phuket-&gt;Similan 50,000-80,000 THB/boat/day (forbesandpartners) = whole-boat, excluded. Premium per-seat anchored ~2,900 THB ($80) net for the longer Phuket origin.</t>
+          <t>Premium slice of Bangkok-Pattaya leisure+EEC road flow; modeled pending operator validation.</t>
         </is>
       </c>
       <c r="AY28" s="44" t="inlineStr">
         <is>
-          <t>Mu Ko Similan NP official visitor statistics (DNP/park clarification, May-2025, via MGR Online https://mgronline.com/uptodate/detail/9680000041761): FY2561(2018)=912,566; FY2562(2019)=676,793; FY2566(2023)=352,701; FY2567(2024)=578,535; FY2568=503,142 as of 30-Apr-2025. Daily cap 3,850 visitors/day (DNP, http://news.dnp.go.th/news/7966). Season: park CLOSED ~May 16 - Oct 14; open season ~212 days/yr (reopened 15-Oct each year, prd.go.th).</t>
+          <t>Premium slice of Bangkok-Pattaya leisure+EEC road flow; modeled pending operator validation.</t>
         </is>
       </c>
     </row>
@@ -7724,11 +7724,11 @@
         </is>
       </c>
       <c r="C11" s="39" t="n">
-        <v>0.1056</v>
+        <v>0.1</v>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>New-entrant ~11% share of today's pool (= the published floor).</t>
+          <t>New-entrant ~10% share of today's pool (= the published floor).</t>
         </is>
       </c>
     </row>
@@ -7801,7 +7801,7 @@
     <row r="18">
       <c r="A18" s="25" t="inlineStr">
         <is>
-          <t>SOM full network (~11% capture, today, +greenfield)</t>
+          <t>SOM full network (~10% capture, today, +greenfield)</t>
         </is>
       </c>
       <c r="B18" s="50">
@@ -7818,7 +7818,7 @@
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>Floor posture (~11% captive capture, today's demand) extended across the whole mapped network.</t>
+          <t>Floor posture (~10% captive capture, today's demand) extended across the whole mapped network.</t>
         </is>
       </c>
     </row>
